--- a/技术文档/射频通信协议.xlsx
+++ b/技术文档/射频通信协议.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
   <si>
     <t>BYTE1</t>
   </si>
@@ -131,6 +131,21 @@
   </si>
   <si>
     <t>帧尾</t>
+  </si>
+  <si>
+    <t>遥控器KFS设置帧</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>指示KFS设置帧</t>
+  </si>
+  <si>
+    <t>高四位为索引为1的位置，低四位为索引为0位置</t>
+  </si>
+  <si>
+    <t>高四位为索引为3的位置，低四位为索引为2位置</t>
   </si>
   <si>
     <t>机器人回传帧</t>
@@ -782,11 +797,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1310,9 +1334,46 @@
         <v>33</v>
       </c>
     </row>
+    <row r="3" spans="1:29">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1">
+        <v>66</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
     <row r="4" spans="1:29">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="1">
         <v>55</v>
@@ -1330,61 +1391,61 @@
         <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="T4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="V4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>19</v>
@@ -1393,7 +1454,7 @@
         <v>31</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AC4" s="1" t="s">
         <v>33</v>

--- a/技术文档/射频通信协议.xlsx
+++ b/技术文档/射频通信协议.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="25605" windowHeight="12060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="68">
   <si>
     <t>BYTE1</t>
   </si>
@@ -76,6 +76,18 @@
     <t>BYTE14</t>
   </si>
   <si>
+    <t>BYTE15</t>
+  </si>
+  <si>
+    <t>BYTE16</t>
+  </si>
+  <si>
+    <t>BYTE17</t>
+  </si>
+  <si>
+    <t>BYTE18</t>
+  </si>
+  <si>
     <t>遥控器数据帧</t>
   </si>
   <si>
@@ -124,6 +136,12 @@
     <t>按键状态高八位</t>
   </si>
   <si>
+    <t>00-04</t>
+  </si>
+  <si>
+    <t>串口屏页面编号</t>
+  </si>
+  <si>
     <t>crc校验</t>
   </si>
   <si>
@@ -139,7 +157,7 @@
     <t>01</t>
   </si>
   <si>
-    <t>指示KFS设置帧</t>
+    <t>指示KFS设置帧的对象</t>
   </si>
   <si>
     <t>高四位为索引为1的位置，低四位为索引为0位置</t>
@@ -148,6 +166,21 @@
     <t>高四位为索引为3的位置，低四位为索引为2位置</t>
   </si>
   <si>
+    <t>串口屏命令转发帧</t>
+  </si>
+  <si>
+    <t>命令码</t>
+  </si>
+  <si>
+    <t>发送次数累计值（0~255）</t>
+  </si>
+  <si>
+    <t>00</t>
+  </si>
+  <si>
+    <t>保留扩展（置空）</t>
+  </si>
+  <si>
     <t>机器人回传帧</t>
   </si>
   <si>
@@ -179,6 +212,24 @@
   </si>
   <si>
     <t>机器人命令2</t>
+  </si>
+  <si>
+    <t>R1打算拿取的KFS（高4位=索引1，低4位=索引0）</t>
+  </si>
+  <si>
+    <t>00-0F</t>
+  </si>
+  <si>
+    <t>R1打算拿取的KFS（低4位=索引3）</t>
+  </si>
+  <si>
+    <t>00-07</t>
+  </si>
+  <si>
+    <t>武器头夹取状态 (0x00~0x07)</t>
+  </si>
+  <si>
+    <t>KFS储存区</t>
   </si>
   <si>
     <t>ED</t>
@@ -807,10 +858,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1124,42 +1178,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:AK5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.375" style="1" customWidth="1"/>
     <col min="3" max="3" width="6.125" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.375" style="1" customWidth="1"/>
     <col min="5" max="5" width="6.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="7" max="7" width="18.075" style="1" customWidth="1"/>
     <col min="8" max="8" width="6.375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="1" customWidth="1"/>
+    <col min="9" max="9" width="44.375" style="1" customWidth="1"/>
     <col min="10" max="10" width="6.375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
+    <col min="11" max="11" width="44.375" style="1" customWidth="1"/>
     <col min="12" max="12" width="6.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12" style="1" customWidth="1"/>
     <col min="14" max="14" width="6.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="1" customWidth="1"/>
     <col min="16" max="16" width="6.375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10" style="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" customWidth="1"/>
     <col min="18" max="18" width="6.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.125" style="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="10" style="1" customWidth="1"/>
+    <col min="21" max="21" width="15" style="1" customWidth="1"/>
     <col min="22" max="22" width="7.375" style="1" customWidth="1"/>
     <col min="23" max="23" width="15" style="1" customWidth="1"/>
     <col min="24" max="24" width="7.375" style="1" customWidth="1"/>
     <col min="25" max="25" width="15" style="1" customWidth="1"/>
     <col min="26" max="26" width="7.375" style="1" customWidth="1"/>
-    <col min="27" max="27" width="8.125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="46" style="1" customWidth="1"/>
     <col min="28" max="28" width="7.375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="5.125" style="1" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="1"/>
+    <col min="29" max="29" width="32.25" style="1" customWidth="1"/>
+    <col min="30" max="30" width="7.375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="28.375" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7.375" style="1" customWidth="1"/>
+    <col min="33" max="33" width="10" style="1" customWidth="1"/>
+    <col min="34" max="34" width="7.375" style="1" customWidth="1"/>
+    <col min="35" max="35" width="8.125" style="1" customWidth="1"/>
+    <col min="36" max="36" width="7.375" style="1" customWidth="1"/>
+    <col min="37" max="37" width="5.125" style="1" customWidth="1"/>
+    <col min="38" max="16382" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:37">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1244,220 +1306,321 @@
       <c r="AC1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="AD1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:37">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1">
         <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29">
-      <c r="A3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D3" s="1">
         <v>66</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1">
+        <v>77</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46031</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="N4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="O4" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="4" spans="1:29">
-      <c r="A4" s="1" t="s">
+    <row r="5" spans="1:37">
+      <c r="A5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="1">
+        <v>55</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF5" s="3">
+        <v>46024</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AK5" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="B4" s="1">
-        <v>55</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
